--- a/skill/passiveskill.xlsx
+++ b/skill/passiveskill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -41,12 +41,6 @@
   </si>
   <si>
     <t>describe</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>草上飞行</t>
@@ -1146,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="33.7777777777778" customWidth="1"/>
@@ -1167,157 +1161,143 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>205</v>
-      </c>
-      <c r="B12" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/skill/passiveskill.xlsx
+++ b/skill/passiveskill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>describe</t>
+  </si>
+  <si>
+    <t>config</t>
   </si>
   <si>
     <t>草上飞行</t>
@@ -1140,13 +1143,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="33.7777777777778" customWidth="1"/>
+    <col min="4" max="4" width="53.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1158,6 +1162,9 @@
       </c>
       <c r="D1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1165,27 +1172,30 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1193,69 +1203,81 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>201</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>202</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1263,41 +1285,47 @@
         <v>203</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>204</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>205</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
